--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512408_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512408_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.581899999999999</v>
+        <v>7.0652</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5776</v>
+        <v>4.733</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0043</v>
+        <v>2.3322</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5964</v>
+        <v>6.3787</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4629</v>
+        <v>1.7392</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1335</v>
+        <v>4.6394</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8132</v>
+        <v>4.3992</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6551</v>
+        <v>1.0055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1581</v>
+        <v>3.3937</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7832</v>
+        <v>1.9795</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8078</v>
+        <v>0.7337</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9755</v>
+        <v>1.2458</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2048</v>
+        <v>2.0245</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2291</v>
+        <v>-0.2025</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0242</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7063</v>
+        <v>0.1031</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0253</v>
+        <v>0.5362</v>
       </c>
       <c r="U2" t="n">
-        <v>0.681</v>
+        <v>-0.4331</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4841</v>
+        <v>-1.4411</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4841</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.188</v>
+        <v>6.9673</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4404</v>
+        <v>4.7651</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7476</v>
+        <v>2.2022</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3258</v>
+        <v>5.6139</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7338</v>
+        <v>4.486</v>
       </c>
       <c r="I3" t="n">
-        <v>4.592</v>
+        <v>1.1279</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2919</v>
+        <v>3.8723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9540999999999999</v>
+        <v>3.7133</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3378</v>
+        <v>0.159</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0339</v>
+        <v>1.7416</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2542</v>
+        <v>0.9689</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0485</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2048</v>
+        <v>-1.2147</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2533</v>
+        <v>1.0123</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7635999999999999</v>
+        <v>1.0539</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6466</v>
+        <v>1.1038</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.117</v>
+        <v>-0.0499</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4227</v>
+        <v>0.5019</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0037</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4227</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8202</v>
+        <v>5.4574</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8148</v>
+        <v>3.9159</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0055</v>
+        <v>1.5415</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6975</v>
+        <v>-0.2842</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8822</v>
+        <v>0.2564</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8153</v>
+        <v>-0.5406</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9735</v>
+        <v>-0.3863</v>
       </c>
       <c r="K4" t="n">
-        <v>2.855</v>
+        <v>1.9537</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1185</v>
+        <v>-2.3401</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7239</v>
+        <v>0.1021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0272</v>
+        <v>-1.6973</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6968</v>
+        <v>1.7994</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4339</v>
+        <v>2.0245</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6388</v>
+        <v>2.0245</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.3296</v>
       </c>
       <c r="T4" t="n">
-        <v>0.804</v>
+        <v>0.1365</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8731</v>
+        <v>-0.4661</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2421</v>
+        <v>4.0467</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2421</v>
+        <v>4.1657</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4841</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1286</v>
+        <v>4.6195</v>
       </c>
       <c r="E5" t="n">
-        <v>2.661</v>
+        <v>3.5918</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4677</v>
+        <v>1.0278</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3308</v>
+        <v>3.6972</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2455</v>
+        <v>2.8858</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5763</v>
+        <v>0.8114</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.497</v>
+        <v>3.0226</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8908</v>
+        <v>2.9033</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3878</v>
+        <v>0.1193</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1662</v>
+        <v>0.6746</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6453</v>
+        <v>-0.0175</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8116</v>
+        <v>0.6921</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0485</v>
+        <v>1.4172</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2025</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0485</v>
+        <v>1.6196</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6031</v>
+        <v>-0.2439</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9741</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.629</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>4.0141</v>
+        <v>-0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1321</v>
+        <v>0.2509</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1181</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1075</v>
+        <v>3.4581</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2802</v>
+        <v>5.65</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1727</v>
+        <v>-2.1919</v>
       </c>
       <c r="G6" t="n">
-        <v>3.31</v>
+        <v>3.3396</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3949</v>
+        <v>2.4296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9151</v>
+        <v>0.91</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2863</v>
+        <v>4.365</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2073</v>
+        <v>4.2855</v>
       </c>
       <c r="L6" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.0254</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8125</v>
+        <v>-1.8559</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8361</v>
+        <v>0.8305</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7236</v>
+        <v>0.0713</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2472</v>
+        <v>0.512</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5235</v>
+        <v>-0.4407</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9504</v>
+        <v>-0.9651</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.2265</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6028</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2123</v>
+        <v>0.2673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8003</v>
+        <v>0.7914</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2034</v>
+        <v>0.1979</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5969</v>
+        <v>0.5934</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9958</v>
+        <v>1.0077</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9562</v>
+        <v>0.968</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1954</v>
+        <v>-0.2164</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7529</v>
+        <v>-0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5574</v>
+        <v>0.5537</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6866</v>
+        <v>-0.2557</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.393</v>
+        <v>-0.0485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2936</v>
+        <v>-0.2072</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.438</v>
+        <v>1.0189</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6938</v>
+        <v>-0.1649</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1318</v>
+        <v>1.1838</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8025</v>
+        <v>1.7999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3658</v>
+        <v>1.364</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4368</v>
+        <v>0.4359</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3854</v>
+        <v>1.4411</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9241</v>
+        <v>1.9742</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5387</v>
+        <v>-0.5331</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4172</v>
+        <v>0.3588</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5583</v>
+        <v>-0.6101</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9755</v>
+        <v>0.9689</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7754</v>
+        <v>-0.1963</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0809</v>
+        <v>0.3338</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6945</v>
+        <v>-0.5301</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2302</v>
+        <v>0.2251</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0744</v>
+        <v>1.097</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8442</v>
+        <v>-0.8718</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2968</v>
+        <v>0.1039</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0655</v>
+        <v>-0.7084</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2313</v>
+        <v>0.8123</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1116</v>
+        <v>0.0643</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3903</v>
+        <v>0.2779</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2787</v>
+        <v>-0.2136</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.8468</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.4741</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1116</v>
+        <v>0.9111</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3903</v>
+        <v>-0.1962</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2787</v>
+        <v>1.1073</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2025</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1852</v>
+        <v>-0.3776</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0655</v>
+        <v>-0.161</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1197</v>
+        <v>-0.2166</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3804</v>
+        <v>-0.1689</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2468</v>
+        <v>0.0398</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8665</v>
+        <v>-0.2087</v>
       </c>
       <c r="G10" t="n">
-        <v>0.076</v>
+        <v>-0.1183</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3007</v>
+        <v>-0.3951</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2247</v>
+        <v>0.2768</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8711</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4684</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3395</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9471000000000001</v>
+        <v>-0.1183</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1677</v>
+        <v>-0.3951</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1148</v>
+        <v>0.2768</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2291</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8903</v>
+        <v>-0.0506</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.655</v>
+        <v>0.0398</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2353</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5903</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4841</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3104</v>
+        <v>-0.7729</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.361</v>
+        <v>2.2772</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0506</v>
+        <v>-3.0501</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4411</v>
+        <v>0.3752</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8587</v>
+        <v>0.7507</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2998</v>
+        <v>-0.3755</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.116</v>
+        <v>1.1842</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2764</v>
+        <v>1.8365</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1605</v>
+        <v>-0.6523</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5571</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4178</v>
+        <v>-1.0859</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1394</v>
+        <v>0.2768</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4339</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0485</v>
+        <v>-1.2147</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.3383</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1965</v>
+        <v>-0.0728</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4693</v>
+        <v>-0.2655</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3482</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.3804</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3482</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3544</v>
+        <v>-0.9223</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8176</v>
+        <v>-1.9944</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1719</v>
+        <v>1.0721</v>
       </c>
       <c r="G12" t="n">
-        <v>0.363</v>
+        <v>0.4456</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7416</v>
+        <v>-0.8692</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3785</v>
+        <v>1.3148</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1439</v>
+        <v>-0.0893</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8012</v>
+        <v>-1.2657</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6572</v>
+        <v>1.1764</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7809</v>
+        <v>0.5349</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0596</v>
+        <v>0.3964</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2787</v>
+        <v>0.1384</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8194</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2291</v>
+        <v>-2.0245</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4097</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.898</v>
+        <v>-0.295</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4585</v>
+        <v>0.1193</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4395</v>
+        <v>-0.4143</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3612</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3612</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1071</v>
+        <v>-2.1515</v>
       </c>
       <c r="E13" t="n">
-        <v>0.975</v>
+        <v>0.9647</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0821</v>
+        <v>-3.1162</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0806</v>
+        <v>-0.0977</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9562</v>
+        <v>-0.968</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8756</v>
+        <v>0.8703</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7503</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6888</v>
+        <v>0.7105</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8089</v>
+        <v>-0.848</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6451</v>
+        <v>-1.6785</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8361</v>
+        <v>0.8305</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2609</v>
+        <v>0.2794</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2466</v>
+        <v>0.2144</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0142</v>
+        <v>0.065</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3116</v>
+        <v>-3.3455</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3116</v>
+        <v>-3.3455</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.6301</v>
+        <v>25.9012</v>
       </c>
       <c r="E14" t="n">
-        <v>21.8023</v>
+        <v>24.029</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8283</v>
+        <v>1.8723</v>
       </c>
       <c r="G14" t="n">
-        <v>21.8896</v>
+        <v>22.0056</v>
       </c>
       <c r="H14" t="n">
-        <v>12.1256</v>
+        <v>12.1552</v>
       </c>
       <c r="I14" t="n">
-        <v>9.764199999999999</v>
+        <v>9.850200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>18.1342</v>
+        <v>18.72</v>
       </c>
       <c r="K14" t="n">
-        <v>18.1246</v>
+        <v>18.5589</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009700000000000618</v>
+        <v>0.1610999999999995</v>
       </c>
       <c r="M14" t="n">
-        <v>3.755500000000001</v>
+        <v>3.285500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.9992</v>
+        <v>-6.403700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>9.754800000000001</v>
+        <v>9.689100000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>6.145400000000002</v>
+        <v>6.073599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.218</v>
+        <v>-9.1105</v>
       </c>
       <c r="R14" t="n">
-        <v>15.3635</v>
+        <v>15.184</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8463</v>
+        <v>-0.5793</v>
       </c>
       <c r="T14" t="n">
-        <v>1.853000000000001</v>
+        <v>3.2342</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.6993</v>
+        <v>-3.813499999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5586</v>
+        <v>-1.5988</v>
       </c>
       <c r="W14" t="n">
-        <v>11.033</v>
+        <v>11.1849</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.5916</v>
+        <v>-12.7838</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3702</v>
+        <v>2.047</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3985</v>
+        <v>4.1481</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0283</v>
+        <v>-2.1012</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9127</v>
+        <v>0.905</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4488</v>
+        <v>0.4544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0697</v>
+        <v>3.1206</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0697</v>
+        <v>3.1206</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1569</v>
+        <v>-2.2156</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6208</v>
+        <v>-2.6663</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6753</v>
+        <v>0.3807</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7385</v>
+        <v>0.4324</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0518</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="16">
@@ -1657,28 +1657,28 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5346</v>
+        <v>0.7479</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1044</v>
+        <v>3.2121</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5698</v>
+        <v>-2.4641</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6329</v>
+        <v>-0.6414</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2264</v>
+        <v>1.2256</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8593</v>
+        <v>-1.867</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0321</v>
+        <v>1.0845</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4257</v>
+        <v>2.4687</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3935</v>
+        <v>-1.3842</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.665</v>
+        <v>-1.726</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1992</v>
+        <v>-1.2431</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2532</v>
+        <v>0.4623</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.7109</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4449</v>
+        <v>-0.2486</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5288</v>
+        <v>1.5344</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2275</v>
+        <v>-1.8781</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8005</v>
+        <v>-1.1412</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4271</v>
+        <v>-0.7369</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4304</v>
+        <v>-2.4214</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2679</v>
+        <v>-1.2464</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1625</v>
+        <v>-1.1749</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3509</v>
+        <v>-1.2881</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6541</v>
+        <v>-0.596</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0796</v>
+        <v>-1.1333</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6138</v>
+        <v>-0.6504</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S18" t="n">
-        <v>0.998</v>
+        <v>0.3409</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7552</v>
+        <v>0.3493</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2428</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7366</v>
+        <v>-2.0883</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4591</v>
+        <v>0.1794</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2775</v>
+        <v>-2.2677</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3482</v>
+        <v>-3.3875</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4889</v>
+        <v>-1.5205</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8593</v>
+        <v>-1.867</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6794</v>
+        <v>-0.6348</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4109</v>
+        <v>1.4414</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0903</v>
+        <v>-2.0763</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6688</v>
+        <v>-2.7527</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.8998</v>
+        <v>-2.9619</v>
       </c>
       <c r="O19" t="n">
-        <v>0.231</v>
+        <v>0.2092</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2132</v>
+        <v>0.8703</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1296</v>
+        <v>0.4098</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3429</v>
+        <v>0.4605</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>I. ORDONEZ OCHOA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.789</v>
+        <v>-2.994</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0147</v>
+        <v>-1.8156</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8036</v>
+        <v>-1.1784</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4843</v>
+        <v>-3.4278</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1121</v>
+        <v>-2.8065</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3722</v>
+        <v>-0.6213</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2262</v>
+        <v>-0.7343</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2262</v>
+        <v>-0.0422</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6921</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7106</v>
+        <v>-2.6935</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3383</v>
+        <v>-2.7644</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3722</v>
+        <v>0.0708</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0565</v>
+        <v>0.9767</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5091</v>
+        <v>0.8787</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4526</v>
+        <v>0.098</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3612</v>
+        <v>0.0645</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6965</v>
+        <v>0.0645</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ORDONEZ OCHOA</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3097</v>
+        <v>-3.5009</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0459</v>
+        <v>-1.2254</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2638</v>
+        <v>-2.2755</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4037</v>
+        <v>-4.1149</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7986</v>
+        <v>-2.3508</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6051</v>
+        <v>-1.764</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7907</v>
+        <v>-2.3548</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0939</v>
+        <v>0.4135</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6968</v>
+        <v>-2.7684</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.613</v>
+        <v>-1.76</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7047</v>
+        <v>-2.7644</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0916</v>
+        <v>1.0043</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6145</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-1.2147</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6788999999999999</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7635999999999999</v>
+        <v>-0.194</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0847</v>
+        <v>0.1036</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0297</v>
+        <v>0.5019</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0297</v>
+        <v>2.5381</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3764</v>
+        <v>-3.5812</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1846</v>
+        <v>-0.7653</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1917</v>
+        <v>-2.816</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0881</v>
+        <v>-1.4871</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3223</v>
+        <v>-1.1072</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7658</v>
+        <v>-0.3798</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4047</v>
+        <v>0.2555</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3824</v>
+        <v>0.2555</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.787</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6834</v>
+        <v>-1.7425</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7047</v>
+        <v>-1.3627</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0213</v>
+        <v>-0.3798</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4339</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9772999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.048</v>
+        <v>0.6798</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0707</v>
+        <v>-0.3936</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4841</v>
+        <v>-2.3804</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4971</v>
+        <v>-0.6883</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.013</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="23">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4215</v>
+        <v>-3.6523</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9205</v>
+        <v>-1.2835</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5011</v>
+        <v>-2.3688</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5483</v>
+        <v>-1.5466</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8974</v>
+        <v>-0.8899</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.651</v>
+        <v>-0.6567</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5623</v>
+        <v>-0.5163</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1345</v>
+        <v>0.1758</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.986</v>
+        <v>-1.0303</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0318</v>
+        <v>-1.0657</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5584</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6466</v>
+        <v>-0.1109</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.7071</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9385</v>
+        <v>0.9393</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8393</v>
+        <v>-4.4225</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1094</v>
+        <v>-2.6223</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7299</v>
+        <v>-1.8002</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3437</v>
+        <v>-3.7052</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3895</v>
+        <v>-1.6997</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0458</v>
+        <v>-2.0055</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4932</v>
+        <v>-1.9577</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7965</v>
+        <v>-1.2657</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8505</v>
+        <v>-1.7474</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.5931</v>
+        <v>-0.4341</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7426</v>
+        <v>-1.3134</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.4582</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2776</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8194</v>
+        <v>0.4049</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2047</v>
+        <v>-0.1099</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2388</v>
+        <v>0.3477</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0341</v>
+        <v>-0.4576</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0059</v>
+        <v>-5.7913</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1772</v>
+        <v>-2.934</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8287</v>
+        <v>-2.8573</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.6934</v>
+        <v>-3.364</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6948</v>
+        <v>-3.3995</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9987</v>
+        <v>0.0354</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9732</v>
+        <v>-1.4454</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2764</v>
+        <v>-0.7534</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7203</v>
+        <v>-1.9186</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4183</v>
+        <v>-2.6461</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.3019</v>
+        <v>0.7275</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6145</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0242</v>
+        <v>-3.2392</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4097</v>
+        <v>0.8098</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6979</v>
+        <v>0.2531</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1798</v>
+        <v>0.3095</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5181</v>
+        <v>-0.0565</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.6302</v>
+        <v>-23.9284</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.008699999999999</v>
+        <v>-3.0624</v>
       </c>
       <c r="F26" t="n">
-        <v>-20.6215</v>
+        <v>-20.8661</v>
       </c>
       <c r="G26" t="n">
-        <v>-21.8894</v>
+        <v>-22.0056</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.1254</v>
+        <v>-12.1552</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.764199999999999</v>
+        <v>-9.850100000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.7555</v>
+        <v>-3.285499999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>5.999400000000001</v>
+        <v>6.403500000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-9.754799999999999</v>
+        <v>-9.689399999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-18.1341</v>
+        <v>-18.7199</v>
       </c>
       <c r="N26" t="n">
-        <v>-18.1245</v>
+        <v>-18.5591</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.009500000000000064</v>
+        <v>-0.1610999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.1454</v>
+        <v>-6.073599999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.3635</v>
+        <v>-15.184</v>
       </c>
       <c r="R26" t="n">
-        <v>9.218000000000002</v>
+        <v>9.1105</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8462</v>
+        <v>2.5519</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6993</v>
+        <v>3.8132</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.853</v>
+        <v>-1.2615</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5584</v>
+        <v>1.599</v>
       </c>
       <c r="W26" t="n">
-        <v>11.4111</v>
+        <v>11.5935</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.852500000000001</v>
+        <v>-9.9947</v>
       </c>
     </row>
   </sheetData>
